--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13 08:28:16</t>
+          <t>2026-09-13 13:51:44</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13 23:28:16</t>
+          <t>2026-09-14 04:51:44</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13 13:51:44</t>
+          <t>2026-09-14 09:09:33</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14 04:51:44</t>
+          <t>2026-09-15 00:09:33</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14 09:09:33</t>
+          <t>2026-09-14 15:57:40</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:09:33</t>
+          <t>2026-09-15 06:57:40</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14 15:57:40</t>
+          <t>2026-09-15 08:51:23</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15 06:57:40</t>
+          <t>2026-09-15 23:51:23</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15 08:51:23</t>
+          <t>2026-09-15 14:23:59</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15 23:51:23</t>
+          <t>2026-09-16 05:23:59</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15 14:23:59</t>
+          <t>2026-09-16 08:45:21</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16 05:23:59</t>
+          <t>2026-09-16 23:45:21</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16 08:45:21</t>
+          <t>2026-09-16 14:16:50</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16 23:45:21</t>
+          <t>2026-09-17 05:16:50</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16 14:16:50</t>
+          <t>2026-09-17 08:49:07</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17 05:16:50</t>
+          <t>2026-09-17 23:49:07</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17 08:49:07</t>
+          <t>2026-09-17 14:22:57</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17 23:49:07</t>
+          <t>2026-09-18 05:22:57</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17 14:22:57</t>
+          <t>2026-09-18 08:24:39</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18 05:22:57</t>
+          <t>2026-09-18 23:24:39</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18 08:24:39</t>
+          <t>2026-09-18 13:43:17</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18 23:24:39</t>
+          <t>2026-09-19 04:43:17</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18 13:43:17</t>
+          <t>2026-09-19 08:12:20</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19 04:43:17</t>
+          <t>2026-09-19 23:12:20</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19 08:12:20</t>
+          <t>2026-09-19 13:16:17</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19 23:12:20</t>
+          <t>2026-09-20 04:16:17</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19 13:16:17</t>
+          <t>2026-09-20 08:44:59</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20 04:16:17</t>
+          <t>2026-09-20 23:44:59</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20 08:44:59</t>
+          <t>2026-09-20 13:39:12</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20 23:44:59</t>
+          <t>2026-09-21 04:39:12</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20 13:39:12</t>
+          <t>2026-09-21 09:11:37</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21 04:39:12</t>
+          <t>2026-09-22 00:11:37</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21 09:11:37</t>
+          <t>2026-09-21 15:59:06</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 00:11:37</t>
+          <t>2026-09-22 06:59:06</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21 15:59:06</t>
+          <t>2026-09-22 08:42:58</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 06:59:06</t>
+          <t>2026-09-22 23:42:58</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 08:42:58</t>
+          <t>2026-09-22 14:08:15</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 23:42:58</t>
+          <t>2026-09-23 05:08:15</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 14:08:15</t>
+          <t>2026-09-23 08:45:01</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 05:08:15</t>
+          <t>2026-09-23 23:45:01</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 08:45:01</t>
+          <t>2026-09-23 14:19:11</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 23:45:01</t>
+          <t>2026-09-24 05:19:11</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 14:19:11</t>
+          <t>2026-09-24 08:39:20</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 05:19:11</t>
+          <t>2026-09-24 23:39:20</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 08:39:20</t>
+          <t>2026-09-24 14:17:41</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 23:39:20</t>
+          <t>2026-09-25 05:17:41</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 14:17:41</t>
+          <t>2026-09-25 09:00:13</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25 05:17:41</t>
+          <t>2026-09-26 00:00:13</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25 09:00:13</t>
+          <t>2026-09-25 14:40:49</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26 00:00:13</t>
+          <t>2026-09-26 05:40:49</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25 14:40:49</t>
+          <t>2026-09-26 08:46:23</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26 05:40:49</t>
+          <t>2026-09-26 23:46:23</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26 08:46:23</t>
+          <t>2026-09-26 13:48:48</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26 23:46:23</t>
+          <t>2026-09-27 04:48:48</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26 13:48:48</t>
+          <t>2026-09-27 09:26:26</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27 04:48:48</t>
+          <t>2026-09-28 00:26:26</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27 09:26:26</t>
+          <t>2026-09-27 14:47:29</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:26:26</t>
+          <t>2026-09-28 05:47:29</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-27 14:47:29</t>
+          <t>2026-09-28 10:03:10</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 05:47:29</t>
+          <t>2026-09-29 01:03:10</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 10:03:10</t>
+          <t>2026-09-29 10:01:54</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:03:10</t>
+          <t>2026-09-30 01:01:54</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29 10:01:54</t>
+          <t>2026-09-30 09:54:42</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 01:01:54</t>
+          <t>2026-10-01 00:54:42</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:54:42</t>
+          <t>2026-10-01 10:21:51</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01 00:54:42</t>
+          <t>2026-10-02 01:21:51</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01 10:21:51</t>
+          <t>2026-10-02 09:58:26</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 01:21:51</t>
+          <t>2026-10-03 00:58:26</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02 09:58:26</t>
+          <t>2026-10-03 09:20:38</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03 00:58:26</t>
+          <t>2026-10-04 00:20:38</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03 09:20:38</t>
+          <t>2026-10-03 14:23:06</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04 00:20:38</t>
+          <t>2026-10-04 05:23:06</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03 14:23:06</t>
+          <t>2026-10-04 09:59:36</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04 05:23:06</t>
+          <t>2026-10-05 00:59:36</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04 09:59:36</t>
+          <t>2026-10-05 10:44:05</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 00:59:36</t>
+          <t>2026-10-06 01:44:05</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 10:44:05</t>
+          <t>2026-10-06 10:37:16</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:44:05</t>
+          <t>2026-10-07 01:37:16</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 10:37:16</t>
+          <t>2026-10-07 10:28:38</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 01:37:16</t>
+          <t>2026-10-08 01:28:38</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 10:28:38</t>
+          <t>2026-10-08 10:49:24</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 01:28:38</t>
+          <t>2026-10-09 01:49:24</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 10:49:24</t>
+          <t>2026-10-09 10:47:58</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09 01:49:24</t>
+          <t>2026-10-10 01:47:58</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09 10:47:58</t>
+          <t>2026-10-10 10:02:50</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 01:47:58</t>
+          <t>2026-10-11 01:02:50</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 10:02:50</t>
+          <t>2026-10-11 10:13:19</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 01:02:50</t>
+          <t>2026-10-12 01:13:19</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 10:13:19</t>
+          <t>2026-10-12 11:11:48</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 01:13:19</t>
+          <t>2026-10-13 02:11:48</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 11:11:48</t>
+          <t>2026-10-13 10:53:16</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 02:11:48</t>
+          <t>2026-10-14 01:53:16</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 10:53:16</t>
+          <t>2026-10-14 08:55:15</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 01:53:16</t>
+          <t>2026-10-14 23:55:15</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 08:55:15</t>
+          <t>2026-10-14 14:36:29</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 23:55:15</t>
+          <t>2026-10-15 05:36:29</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 14:36:29</t>
+          <t>2026-10-15 08:29:45</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 05:36:29</t>
+          <t>2026-10-15 23:29:45</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 08:29:45</t>
+          <t>2026-10-15 14:17:04</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 23:29:45</t>
+          <t>2026-10-16 05:17:04</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 14:17:04</t>
+          <t>2026-10-16 08:23:05</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 05:17:04</t>
+          <t>2026-10-16 23:23:05</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 08:23:05</t>
+          <t>2026-10-16 14:06:19</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 23:23:05</t>
+          <t>2026-10-17 05:06:19</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 14:06:19</t>
+          <t>2026-10-17 07:57:45</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 05:06:19</t>
+          <t>2026-10-17 22:57:45</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 07:57:45</t>
+          <t>2026-10-17 13:05:06</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 22:57:45</t>
+          <t>2026-10-18 04:05:06</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 13:05:06</t>
+          <t>2026-10-18 08:13:07</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 04:05:06</t>
+          <t>2026-10-18 23:13:07</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 08:13:07</t>
+          <t>2026-10-18 13:25:05</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 23:13:07</t>
+          <t>2026-10-19 04:25:05</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 13:25:05</t>
+          <t>2026-10-19 09:10:49</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 04:25:05</t>
+          <t>2026-10-20 00:10:49</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 09:10:49</t>
+          <t>2026-10-19 16:34:51</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:10:49</t>
+          <t>2026-10-20 07:34:51</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 16:34:51</t>
+          <t>2026-10-20 08:46:18</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 07:34:51</t>
+          <t>2026-10-20 23:46:18</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 08:46:18</t>
+          <t>2026-10-20 14:24:55</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 23:46:18</t>
+          <t>2026-10-21 05:24:55</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 14:24:55</t>
+          <t>2026-10-21 08:46:40</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 05:24:55</t>
+          <t>2026-10-21 23:46:40</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 08:46:40</t>
+          <t>2026-10-21 14:34:27</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 23:46:40</t>
+          <t>2026-10-22 05:34:27</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:34:27</t>
+          <t>2026-10-22 08:49:00</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 05:34:27</t>
+          <t>2026-10-22 23:49:00</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 08:49:00</t>
+          <t>2026-10-22 14:36:01</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 23:49:00</t>
+          <t>2026-10-23 05:36:01</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 14:36:01</t>
+          <t>2026-10-23 08:44:28</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 05:36:01</t>
+          <t>2026-10-23 23:44:28</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 08:44:28</t>
+          <t>2026-10-23 14:20:24</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 23:44:28</t>
+          <t>2026-10-24 05:20:24</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 14:20:24</t>
+          <t>2026-10-24 08:19:17</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 05:20:24</t>
+          <t>2026-10-24 23:19:17</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 08:19:17</t>
+          <t>2026-10-24 13:27:41</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 23:19:17</t>
+          <t>2026-10-25 04:27:41</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 13:27:41</t>
+          <t>2026-10-25 08:37:39</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 04:27:41</t>
+          <t>2026-10-25 23:37:39</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 08:37:39</t>
+          <t>2026-10-25 13:49:15</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 23:37:39</t>
+          <t>2026-10-26 04:49:15</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:15</t>
+          <t>2026-10-26 09:13:42</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 04:49:15</t>
+          <t>2026-10-27 00:13:42</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:13:42</t>
+          <t>2026-10-26 16:14:45</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 00:13:42</t>
+          <t>2026-10-27 07:14:45</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 16:14:45</t>
+          <t>2026-10-27 09:20:04</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 07:14:45</t>
+          <t>2026-10-28 00:20:04</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:20:04</t>
+          <t>2026-10-27 15:28:52</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 00:20:04</t>
+          <t>2026-10-28 06:28:52</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 15:28:52</t>
+          <t>2026-10-28 09:54:58</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 06:28:52</t>
+          <t>2026-10-29 00:54:58</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 09:54:58</t>
+          <t>2026-10-29 10:17:36</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 00:54:58</t>
+          <t>2026-10-30 01:17:36</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:17:36</t>
+          <t>2026-10-30 10:19:02</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 01:17:36</t>
+          <t>2026-10-31 01:19:02</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:19:02</t>
+          <t>2026-10-31 09:52:08</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-31 01:19:02</t>
+          <t>2026-11-01 00:52:08</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
